--- a/code/df_tsa_ly.xlsx
+++ b/code/df_tsa_ly.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C500"/>
+  <dimension ref="A1:C509"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1931,7 +1931,7 @@
         <v>2847916</v>
       </c>
       <c r="C136" t="n">
-        <v>36872</v>
+        <v>36871</v>
       </c>
     </row>
     <row r="137">
@@ -1986,7 +1986,7 @@
         <v>2321388</v>
       </c>
       <c r="C141" t="n">
-        <v>30403</v>
+        <v>30402</v>
       </c>
     </row>
     <row r="142">
@@ -2008,7 +2008,7 @@
         <v>2960413</v>
       </c>
       <c r="C143" t="n">
-        <v>42731</v>
+        <v>42729</v>
       </c>
     </row>
     <row r="144">
@@ -2019,7 +2019,7 @@
         <v>3010183</v>
       </c>
       <c r="C144" t="n">
-        <v>48230</v>
+        <v>48229</v>
       </c>
     </row>
     <row r="145">
@@ -2096,7 +2096,7 @@
         <v>2698137</v>
       </c>
       <c r="C151" t="n">
-        <v>42151</v>
+        <v>42141</v>
       </c>
     </row>
     <row r="152">
@@ -2173,7 +2173,7 @@
         <v>2766521</v>
       </c>
       <c r="C158" t="n">
-        <v>41362</v>
+        <v>41361</v>
       </c>
     </row>
     <row r="159">
@@ -2228,7 +2228,7 @@
         <v>2504337</v>
       </c>
       <c r="C163" t="n">
-        <v>32531</v>
+        <v>32521</v>
       </c>
     </row>
     <row r="164">
@@ -2261,7 +2261,7 @@
         <v>2517202</v>
       </c>
       <c r="C166" t="n">
-        <v>35924</v>
+        <v>35923</v>
       </c>
     </row>
     <row r="167">
@@ -2272,7 +2272,7 @@
         <v>2888821</v>
       </c>
       <c r="C167" t="n">
-        <v>42274</v>
+        <v>42273</v>
       </c>
     </row>
     <row r="168">
@@ -2393,7 +2393,7 @@
         <v>2931282</v>
       </c>
       <c r="C178" t="n">
-        <v>41264</v>
+        <v>41263</v>
       </c>
     </row>
     <row r="179">
@@ -2492,7 +2492,7 @@
         <v>2457591</v>
       </c>
       <c r="C187" t="n">
-        <v>37838</v>
+        <v>37835</v>
       </c>
     </row>
     <row r="188">
@@ -2525,7 +2525,7 @@
         <v>2488332</v>
       </c>
       <c r="C190" t="n">
-        <v>37674</v>
+        <v>37672</v>
       </c>
     </row>
     <row r="191">
@@ -2613,7 +2613,7 @@
         <v>2614183</v>
       </c>
       <c r="C198" t="n">
-        <v>35611</v>
+        <v>35610</v>
       </c>
     </row>
     <row r="199">
@@ -2646,7 +2646,7 @@
         <v>2603307</v>
       </c>
       <c r="C201" t="n">
-        <v>37848</v>
+        <v>37845</v>
       </c>
     </row>
     <row r="202">
@@ -2690,7 +2690,7 @@
         <v>2630151</v>
       </c>
       <c r="C205" t="n">
-        <v>36664</v>
+        <v>36662</v>
       </c>
     </row>
     <row r="206">
@@ -2701,7 +2701,7 @@
         <v>2968866</v>
       </c>
       <c r="C206" t="n">
-        <v>44422</v>
+        <v>44421</v>
       </c>
     </row>
     <row r="207">
@@ -2745,7 +2745,7 @@
         <v>2929749</v>
       </c>
       <c r="C210" t="n">
-        <v>45188</v>
+        <v>45187</v>
       </c>
     </row>
     <row r="211">
@@ -2778,7 +2778,7 @@
         <v>2882829</v>
       </c>
       <c r="C213" t="n">
-        <v>41873</v>
+        <v>41872</v>
       </c>
     </row>
     <row r="214">
@@ -2833,7 +2833,7 @@
         <v>2364019</v>
       </c>
       <c r="C218" t="n">
-        <v>32657</v>
+        <v>32656</v>
       </c>
     </row>
     <row r="219">
@@ -2910,7 +2910,7 @@
         <v>2256579</v>
       </c>
       <c r="C225" t="n">
-        <v>30804</v>
+        <v>30803</v>
       </c>
     </row>
     <row r="226">
@@ -3097,7 +3097,7 @@
         <v>2971455</v>
       </c>
       <c r="C242" t="n">
-        <v>48098</v>
+        <v>48096</v>
       </c>
     </row>
     <row r="243">
@@ -3196,7 +3196,7 @@
         <v>2673762</v>
       </c>
       <c r="C251" t="n">
-        <v>39622</v>
+        <v>39621</v>
       </c>
     </row>
     <row r="252">
@@ -3207,7 +3207,7 @@
         <v>2456693</v>
       </c>
       <c r="C252" t="n">
-        <v>33634</v>
+        <v>33633</v>
       </c>
     </row>
     <row r="253">
@@ -3548,7 +3548,7 @@
         <v>2975982</v>
       </c>
       <c r="C283" t="n">
-        <v>40828</v>
+        <v>40827</v>
       </c>
     </row>
     <row r="284">
@@ -3801,7 +3801,7 @@
         <v>2029708</v>
       </c>
       <c r="C306" t="n">
-        <v>32318</v>
+        <v>32317</v>
       </c>
     </row>
     <row r="307">
@@ -3878,7 +3878,7 @@
         <v>2080116</v>
       </c>
       <c r="C313" t="n">
-        <v>32173</v>
+        <v>32172</v>
       </c>
     </row>
     <row r="314">
@@ -3889,7 +3889,7 @@
         <v>2631788</v>
       </c>
       <c r="C314" t="n">
-        <v>41776</v>
+        <v>41775</v>
       </c>
     </row>
     <row r="315">
@@ -4010,7 +4010,7 @@
         <v>2493511</v>
       </c>
       <c r="C325" t="n">
-        <v>33246</v>
+        <v>33245</v>
       </c>
     </row>
     <row r="326">
@@ -4021,7 +4021,7 @@
         <v>2792495</v>
       </c>
       <c r="C326" t="n">
-        <v>38814</v>
+        <v>38812</v>
       </c>
     </row>
     <row r="327">
@@ -4054,7 +4054,7 @@
         <v>2563877</v>
       </c>
       <c r="C329" t="n">
-        <v>43553</v>
+        <v>43550</v>
       </c>
     </row>
     <row r="330">
@@ -4098,7 +4098,7 @@
         <v>2392036</v>
       </c>
       <c r="C333" t="n">
-        <v>39602</v>
+        <v>39601</v>
       </c>
     </row>
     <row r="334">
@@ -4109,7 +4109,7 @@
         <v>2696816</v>
       </c>
       <c r="C334" t="n">
-        <v>40429</v>
+        <v>40427</v>
       </c>
     </row>
     <row r="335">
@@ -4120,7 +4120,7 @@
         <v>3134613</v>
       </c>
       <c r="C335" t="n">
-        <v>49350</v>
+        <v>49348</v>
       </c>
     </row>
     <row r="336">
@@ -4142,7 +4142,7 @@
         <v>2233828</v>
       </c>
       <c r="C337" t="n">
-        <v>28832</v>
+        <v>28828</v>
       </c>
     </row>
     <row r="338">
@@ -4285,7 +4285,7 @@
         <v>2503757</v>
       </c>
       <c r="C350" t="n">
-        <v>39368</v>
+        <v>39367</v>
       </c>
     </row>
     <row r="351">
@@ -4296,7 +4296,7 @@
         <v>2047653</v>
       </c>
       <c r="C351" t="n">
-        <v>27775</v>
+        <v>27776</v>
       </c>
     </row>
     <row r="352">
@@ -4351,7 +4351,7 @@
         <v>2769228</v>
       </c>
       <c r="C356" t="n">
-        <v>44867</v>
+        <v>44866</v>
       </c>
     </row>
     <row r="357">
@@ -4406,7 +4406,7 @@
         <v>2716278</v>
       </c>
       <c r="C361" t="n">
-        <v>44389</v>
+        <v>44388</v>
       </c>
     </row>
     <row r="362">
@@ -4417,7 +4417,7 @@
         <v>2804814</v>
       </c>
       <c r="C362" t="n">
-        <v>42149</v>
+        <v>42148</v>
       </c>
     </row>
     <row r="363">
@@ -4483,7 +4483,7 @@
         <v>2578209</v>
       </c>
       <c r="C368" t="n">
-        <v>44437</v>
+        <v>44435</v>
       </c>
     </row>
     <row r="369">
@@ -4527,7 +4527,7 @@
         <v>1941589</v>
       </c>
       <c r="C372" t="n">
-        <v>27214</v>
+        <v>27213</v>
       </c>
     </row>
     <row r="373">
@@ -4549,7 +4549,7 @@
         <v>2151117</v>
       </c>
       <c r="C374" t="n">
-        <v>29490</v>
+        <v>29488</v>
       </c>
     </row>
     <row r="375">
@@ -4604,7 +4604,7 @@
         <v>1688866</v>
       </c>
       <c r="C379" t="n">
-        <v>20169</v>
+        <v>20168</v>
       </c>
     </row>
     <row r="380">
@@ -4615,7 +4615,7 @@
         <v>1903860</v>
       </c>
       <c r="C380" t="n">
-        <v>22198</v>
+        <v>22196</v>
       </c>
     </row>
     <row r="381">
@@ -4626,7 +4626,7 @@
         <v>2460511</v>
       </c>
       <c r="C381" t="n">
-        <v>32235</v>
+        <v>32234</v>
       </c>
     </row>
     <row r="382">
@@ -4637,7 +4637,7 @@
         <v>2608430</v>
       </c>
       <c r="C382" t="n">
-        <v>34647</v>
+        <v>34646</v>
       </c>
     </row>
     <row r="383">
@@ -4659,7 +4659,7 @@
         <v>2231469</v>
       </c>
       <c r="C384" t="n">
-        <v>35393</v>
+        <v>35392</v>
       </c>
     </row>
     <row r="385">
@@ -4681,7 +4681,7 @@
         <v>1952569</v>
       </c>
       <c r="C386" t="n">
-        <v>23829</v>
+        <v>23828</v>
       </c>
     </row>
     <row r="387">
@@ -4714,7 +4714,7 @@
         <v>2243481</v>
       </c>
       <c r="C389" t="n">
-        <v>30630</v>
+        <v>30629</v>
       </c>
     </row>
     <row r="390">
@@ -4736,7 +4736,7 @@
         <v>1313323</v>
       </c>
       <c r="C391" t="n">
-        <v>29043</v>
+        <v>29042</v>
       </c>
     </row>
     <row r="392">
@@ -4747,7 +4747,7 @@
         <v>1830079</v>
       </c>
       <c r="C392" t="n">
-        <v>27150</v>
+        <v>27149</v>
       </c>
     </row>
     <row r="393">
@@ -4769,7 +4769,7 @@
         <v>1879610</v>
       </c>
       <c r="C394" t="n">
-        <v>21689</v>
+        <v>21687</v>
       </c>
     </row>
     <row r="395">
@@ -4846,7 +4846,7 @@
         <v>1839311</v>
       </c>
       <c r="C401" t="n">
-        <v>20177</v>
+        <v>20175</v>
       </c>
     </row>
     <row r="402">
@@ -4857,7 +4857,7 @@
         <v>2324236</v>
       </c>
       <c r="C402" t="n">
-        <v>28063</v>
+        <v>28062</v>
       </c>
     </row>
     <row r="403">
@@ -4868,7 +4868,7 @@
         <v>2351379</v>
       </c>
       <c r="C403" t="n">
-        <v>32225</v>
+        <v>32224</v>
       </c>
     </row>
     <row r="404">
@@ -4879,7 +4879,7 @@
         <v>1873708</v>
       </c>
       <c r="C404" t="n">
-        <v>25175</v>
+        <v>25173</v>
       </c>
     </row>
     <row r="405">
@@ -4901,7 +4901,7 @@
         <v>2386224</v>
       </c>
       <c r="C406" t="n">
-        <v>30009</v>
+        <v>30008</v>
       </c>
     </row>
     <row r="407">
@@ -4923,7 +4923,7 @@
         <v>2074130</v>
       </c>
       <c r="C408" t="n">
-        <v>24928</v>
+        <v>24927</v>
       </c>
     </row>
     <row r="409">
@@ -4934,7 +4934,7 @@
         <v>2701700</v>
       </c>
       <c r="C409" t="n">
-        <v>35305</v>
+        <v>35303</v>
       </c>
     </row>
     <row r="410">
@@ -4967,7 +4967,7 @@
         <v>2536292</v>
       </c>
       <c r="C412" t="n">
-        <v>41086</v>
+        <v>41085</v>
       </c>
     </row>
     <row r="413">
@@ -5000,7 +5000,7 @@
         <v>2229730</v>
       </c>
       <c r="C415" t="n">
-        <v>29304</v>
+        <v>29302</v>
       </c>
     </row>
     <row r="416">
@@ -5011,7 +5011,7 @@
         <v>2644354</v>
       </c>
       <c r="C416" t="n">
-        <v>35238</v>
+        <v>35236</v>
       </c>
     </row>
     <row r="417">
@@ -5033,7 +5033,7 @@
         <v>2284819</v>
       </c>
       <c r="C418" t="n">
-        <v>31397</v>
+        <v>31396</v>
       </c>
     </row>
     <row r="419">
@@ -5055,7 +5055,7 @@
         <v>1996320</v>
       </c>
       <c r="C420" t="n">
-        <v>33087</v>
+        <v>33086</v>
       </c>
     </row>
     <row r="421">
@@ -5066,7 +5066,7 @@
         <v>1958051</v>
       </c>
       <c r="C421" t="n">
-        <v>24627</v>
+        <v>24625</v>
       </c>
     </row>
     <row r="422">
@@ -5077,7 +5077,7 @@
         <v>2258729</v>
       </c>
       <c r="C422" t="n">
-        <v>26335</v>
+        <v>26334</v>
       </c>
     </row>
     <row r="423">
@@ -5099,7 +5099,7 @@
         <v>2625251</v>
       </c>
       <c r="C424" t="n">
-        <v>36250</v>
+        <v>36249</v>
       </c>
     </row>
     <row r="425">
@@ -5132,7 +5132,7 @@
         <v>2432452</v>
       </c>
       <c r="C427" t="n">
-        <v>33405</v>
+        <v>33403</v>
       </c>
     </row>
     <row r="428">
@@ -5143,7 +5143,7 @@
         <v>1910452</v>
       </c>
       <c r="C428" t="n">
-        <v>23660</v>
+        <v>23659</v>
       </c>
     </row>
     <row r="429">
@@ -5154,7 +5154,7 @@
         <v>2133462</v>
       </c>
       <c r="C429" t="n">
-        <v>25149</v>
+        <v>25146</v>
       </c>
     </row>
     <row r="430">
@@ -5165,7 +5165,7 @@
         <v>2615896</v>
       </c>
       <c r="C430" t="n">
-        <v>33293</v>
+        <v>33291</v>
       </c>
     </row>
     <row r="431">
@@ -5187,7 +5187,7 @@
         <v>2338542</v>
       </c>
       <c r="C432" t="n">
-        <v>32535</v>
+        <v>32534</v>
       </c>
     </row>
     <row r="433">
@@ -5198,7 +5198,7 @@
         <v>2781523</v>
       </c>
       <c r="C433" t="n">
-        <v>38771</v>
+        <v>38769</v>
       </c>
     </row>
     <row r="434">
@@ -5209,7 +5209,7 @@
         <v>2563627</v>
       </c>
       <c r="C434" t="n">
-        <v>35808</v>
+        <v>35807</v>
       </c>
     </row>
     <row r="435">
@@ -5220,7 +5220,7 @@
         <v>2056174</v>
       </c>
       <c r="C435" t="n">
-        <v>27726</v>
+        <v>27725</v>
       </c>
     </row>
     <row r="436">
@@ -5231,7 +5231,7 @@
         <v>2372082</v>
       </c>
       <c r="C436" t="n">
-        <v>30367</v>
+        <v>30366</v>
       </c>
     </row>
     <row r="437">
@@ -5242,7 +5242,7 @@
         <v>2788748</v>
       </c>
       <c r="C437" t="n">
-        <v>38463</v>
+        <v>38462</v>
       </c>
     </row>
     <row r="438">
@@ -5253,7 +5253,7 @@
         <v>2854704</v>
       </c>
       <c r="C438" t="n">
-        <v>40518</v>
+        <v>40510</v>
       </c>
     </row>
     <row r="439">
@@ -5264,7 +5264,7 @@
         <v>2568085</v>
       </c>
       <c r="C439" t="n">
-        <v>35799</v>
+        <v>35795</v>
       </c>
     </row>
     <row r="440">
@@ -5275,7 +5275,7 @@
         <v>2765657</v>
       </c>
       <c r="C440" t="n">
-        <v>41594</v>
+        <v>41584</v>
       </c>
     </row>
     <row r="441">
@@ -5286,7 +5286,7 @@
         <v>2474964</v>
       </c>
       <c r="C441" t="n">
-        <v>42434</v>
+        <v>42431</v>
       </c>
     </row>
     <row r="442">
@@ -5297,7 +5297,7 @@
         <v>2424806</v>
       </c>
       <c r="C442" t="n">
-        <v>33974</v>
+        <v>33968</v>
       </c>
     </row>
     <row r="443">
@@ -5308,7 +5308,7 @@
         <v>2573056</v>
       </c>
       <c r="C443" t="n">
-        <v>34774</v>
+        <v>34769</v>
       </c>
     </row>
     <row r="444">
@@ -5319,7 +5319,7 @@
         <v>2817785</v>
       </c>
       <c r="C444" t="n">
-        <v>40129</v>
+        <v>40120</v>
       </c>
     </row>
     <row r="445">
@@ -5330,7 +5330,7 @@
         <v>2766291</v>
       </c>
       <c r="C445" t="n">
-        <v>41649</v>
+        <v>41648</v>
       </c>
     </row>
     <row r="446">
@@ -5341,7 +5341,7 @@
         <v>2498514</v>
       </c>
       <c r="C446" t="n">
-        <v>35305</v>
+        <v>35303</v>
       </c>
     </row>
     <row r="447">
@@ -5352,7 +5352,7 @@
         <v>2865969</v>
       </c>
       <c r="C447" t="n">
-        <v>41048</v>
+        <v>41044</v>
       </c>
     </row>
     <row r="448">
@@ -5363,7 +5363,7 @@
         <v>2641500</v>
       </c>
       <c r="C448" t="n">
-        <v>39571</v>
+        <v>39561</v>
       </c>
     </row>
     <row r="449">
@@ -5374,7 +5374,7 @@
         <v>2193195</v>
       </c>
       <c r="C449" t="n">
-        <v>30763</v>
+        <v>30756</v>
       </c>
     </row>
     <row r="450">
@@ -5385,7 +5385,7 @@
         <v>2379710</v>
       </c>
       <c r="C450" t="n">
-        <v>31352</v>
+        <v>31349</v>
       </c>
     </row>
     <row r="451">
@@ -5396,7 +5396,7 @@
         <v>2723798</v>
       </c>
       <c r="C451" t="n">
-        <v>36657</v>
+        <v>36655</v>
       </c>
     </row>
     <row r="452">
@@ -5407,7 +5407,7 @@
         <v>2744893</v>
       </c>
       <c r="C452" t="n">
-        <v>39201</v>
+        <v>39191</v>
       </c>
     </row>
     <row r="453">
@@ -5418,7 +5418,7 @@
         <v>2426467</v>
       </c>
       <c r="C453" t="n">
-        <v>33925</v>
+        <v>33920</v>
       </c>
     </row>
     <row r="454">
@@ -5429,7 +5429,7 @@
         <v>2758600</v>
       </c>
       <c r="C454" t="n">
-        <v>39981</v>
+        <v>39977</v>
       </c>
     </row>
     <row r="455">
@@ -5440,7 +5440,7 @@
         <v>2533621</v>
       </c>
       <c r="C455" t="n">
-        <v>38756</v>
+        <v>38748</v>
       </c>
     </row>
     <row r="456">
@@ -5451,7 +5451,7 @@
         <v>2154213</v>
       </c>
       <c r="C456" t="n">
-        <v>30913</v>
+        <v>30911</v>
       </c>
     </row>
     <row r="457">
@@ -5462,7 +5462,7 @@
         <v>2360739</v>
       </c>
       <c r="C457" t="n">
-        <v>33362</v>
+        <v>33359</v>
       </c>
     </row>
     <row r="458">
@@ -5473,7 +5473,7 @@
         <v>2710611</v>
       </c>
       <c r="C458" t="n">
-        <v>39237</v>
+        <v>39226</v>
       </c>
     </row>
     <row r="459">
@@ -5484,7 +5484,7 @@
         <v>2659561</v>
       </c>
       <c r="C459" t="n">
-        <v>40928</v>
+        <v>40914</v>
       </c>
     </row>
     <row r="460">
@@ -5495,7 +5495,7 @@
         <v>2274101</v>
       </c>
       <c r="C460" t="n">
-        <v>34254</v>
+        <v>34246</v>
       </c>
     </row>
     <row r="461">
@@ -5506,7 +5506,7 @@
         <v>2561932</v>
       </c>
       <c r="C461" t="n">
-        <v>39374</v>
+        <v>39364</v>
       </c>
     </row>
     <row r="462">
@@ -5517,7 +5517,7 @@
         <v>2705640</v>
       </c>
       <c r="C462" t="n">
-        <v>39234</v>
+        <v>39229</v>
       </c>
     </row>
     <row r="463">
@@ -5528,7 +5528,7 @@
         <v>2207180</v>
       </c>
       <c r="C463" t="n">
-        <v>30993</v>
+        <v>30980</v>
       </c>
     </row>
     <row r="464">
@@ -5539,7 +5539,7 @@
         <v>2278770</v>
       </c>
       <c r="C464" t="n">
-        <v>31502</v>
+        <v>31497</v>
       </c>
     </row>
     <row r="465">
@@ -5550,7 +5550,7 @@
         <v>2691308</v>
       </c>
       <c r="C465" t="n">
-        <v>38951</v>
+        <v>38945</v>
       </c>
     </row>
     <row r="466">
@@ -5561,7 +5561,7 @@
         <v>2688395</v>
       </c>
       <c r="C466" t="n">
-        <v>40356</v>
+        <v>40351</v>
       </c>
     </row>
     <row r="467">
@@ -5572,7 +5572,7 @@
         <v>2269365</v>
       </c>
       <c r="C467" t="n">
-        <v>34324</v>
+        <v>34315</v>
       </c>
     </row>
     <row r="468">
@@ -5583,7 +5583,7 @@
         <v>2822290</v>
       </c>
       <c r="C468" t="n">
-        <v>40344</v>
+        <v>40338</v>
       </c>
     </row>
     <row r="469">
@@ -5594,7 +5594,7 @@
         <v>2606811</v>
       </c>
       <c r="C469" t="n">
-        <v>36829</v>
+        <v>36816</v>
       </c>
     </row>
     <row r="470">
@@ -5605,7 +5605,7 @@
         <v>2044781</v>
       </c>
       <c r="C470" t="n">
-        <v>27380</v>
+        <v>27357</v>
       </c>
     </row>
     <row r="471">
@@ -5616,7 +5616,7 @@
         <v>2251197</v>
       </c>
       <c r="C471" t="n">
-        <v>28703</v>
+        <v>28680</v>
       </c>
     </row>
     <row r="472">
@@ -5627,7 +5627,7 @@
         <v>2738409</v>
       </c>
       <c r="C472" t="n">
-        <v>36526</v>
+        <v>36507</v>
       </c>
     </row>
     <row r="473">
@@ -5638,7 +5638,7 @@
         <v>2705217</v>
       </c>
       <c r="C473" t="n">
-        <v>40595</v>
+        <v>40580</v>
       </c>
     </row>
     <row r="474">
@@ -5649,7 +5649,7 @@
         <v>2069600</v>
       </c>
       <c r="C474" t="n">
-        <v>31049</v>
+        <v>31022</v>
       </c>
     </row>
     <row r="475">
@@ -5660,7 +5660,7 @@
         <v>2796984</v>
       </c>
       <c r="C475" t="n">
-        <v>41042</v>
+        <v>41018</v>
       </c>
     </row>
     <row r="476">
@@ -5671,7 +5671,7 @@
         <v>2571543</v>
       </c>
       <c r="C476" t="n">
-        <v>38006</v>
+        <v>37985</v>
       </c>
     </row>
     <row r="477">
@@ -5682,7 +5682,7 @@
         <v>2055863</v>
       </c>
       <c r="C477" t="n">
-        <v>27288</v>
+        <v>27278</v>
       </c>
     </row>
     <row r="478">
@@ -5693,7 +5693,7 @@
         <v>2302381</v>
       </c>
       <c r="C478" t="n">
-        <v>29515</v>
+        <v>29501</v>
       </c>
     </row>
     <row r="479">
@@ -5704,7 +5704,7 @@
         <v>2740418</v>
       </c>
       <c r="C479" t="n">
-        <v>37722</v>
+        <v>37707</v>
       </c>
     </row>
     <row r="480">
@@ -5715,7 +5715,7 @@
         <v>2704682</v>
       </c>
       <c r="C480" t="n">
-        <v>40512</v>
+        <v>40500</v>
       </c>
     </row>
     <row r="481">
@@ -5726,7 +5726,7 @@
         <v>2093949</v>
       </c>
       <c r="C481" t="n">
-        <v>31132</v>
+        <v>31127</v>
       </c>
     </row>
     <row r="482">
@@ -5737,7 +5737,7 @@
         <v>2768606</v>
       </c>
       <c r="C482" t="n">
-        <v>41355</v>
+        <v>41342</v>
       </c>
     </row>
     <row r="483">
@@ -5748,7 +5748,7 @@
         <v>2539040</v>
       </c>
       <c r="C483" t="n">
-        <v>37834</v>
+        <v>37818</v>
       </c>
     </row>
     <row r="484">
@@ -5759,7 +5759,7 @@
         <v>2020266</v>
       </c>
       <c r="C484" t="n">
-        <v>27245</v>
+        <v>27237</v>
       </c>
     </row>
     <row r="485">
@@ -5770,7 +5770,7 @@
         <v>2264608</v>
       </c>
       <c r="C485" t="n">
-        <v>27665</v>
+        <v>27658</v>
       </c>
     </row>
     <row r="486">
@@ -5781,7 +5781,7 @@
         <v>2748380</v>
       </c>
       <c r="C486" t="n">
-        <v>36537</v>
+        <v>36534</v>
       </c>
     </row>
     <row r="487">
@@ -5792,7 +5792,7 @@
         <v>2643938</v>
       </c>
       <c r="C487" t="n">
-        <v>39817</v>
+        <v>39810</v>
       </c>
     </row>
     <row r="488">
@@ -5803,7 +5803,7 @@
         <v>2042664</v>
       </c>
       <c r="C488" t="n">
-        <v>31105</v>
+        <v>31103</v>
       </c>
     </row>
     <row r="489">
@@ -5814,7 +5814,7 @@
         <v>2741375</v>
       </c>
       <c r="C489" t="n">
-        <v>39840</v>
+        <v>39830</v>
       </c>
     </row>
     <row r="490">
@@ -5825,7 +5825,7 @@
         <v>2540806</v>
       </c>
       <c r="C490" t="n">
-        <v>35937</v>
+        <v>35930</v>
       </c>
     </row>
     <row r="491">
@@ -5836,7 +5836,7 @@
         <v>2040845</v>
       </c>
       <c r="C491" t="n">
-        <v>27850</v>
+        <v>27842</v>
       </c>
     </row>
     <row r="492">
@@ -5847,7 +5847,7 @@
         <v>2251410</v>
       </c>
       <c r="C492" t="n">
-        <v>30119</v>
+        <v>30101</v>
       </c>
     </row>
     <row r="493">
@@ -5858,7 +5858,7 @@
         <v>2701890</v>
       </c>
       <c r="C493" t="n">
-        <v>39286</v>
+        <v>39265</v>
       </c>
     </row>
     <row r="494">
@@ -5869,7 +5869,7 @@
         <v>2569907</v>
       </c>
       <c r="C494" t="n">
-        <v>40980</v>
+        <v>40969</v>
       </c>
     </row>
     <row r="495">
@@ -5880,7 +5880,7 @@
         <v>2088463</v>
       </c>
       <c r="C495" t="n">
-        <v>32960</v>
+        <v>32954</v>
       </c>
     </row>
     <row r="496">
@@ -5891,7 +5891,7 @@
         <v>2587640</v>
       </c>
       <c r="C496" t="n">
-        <v>41486</v>
+        <v>41465</v>
       </c>
     </row>
     <row r="497">
@@ -5902,7 +5902,7 @@
         <v>2661314</v>
       </c>
       <c r="C497" t="n">
-        <v>39750</v>
+        <v>39722</v>
       </c>
     </row>
     <row r="498">
@@ -5913,7 +5913,7 @@
         <v>2143904</v>
       </c>
       <c r="C498" t="n">
-        <v>30851</v>
+        <v>30818</v>
       </c>
     </row>
     <row r="499">
@@ -5924,7 +5924,7 @@
         <v>2399389</v>
       </c>
       <c r="C499" t="n">
-        <v>33113</v>
+        <v>33087</v>
       </c>
     </row>
     <row r="500">
@@ -5935,7 +5935,106 @@
         <v>2858330</v>
       </c>
       <c r="C500" t="n">
-        <v>39988</v>
+        <v>39957</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B501" t="n">
+        <v>2796834</v>
+      </c>
+      <c r="C501" t="n">
+        <v>42837</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B502" t="n">
+        <v>2260950</v>
+      </c>
+      <c r="C502" t="n">
+        <v>36652</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B503" t="n">
+        <v>2887942</v>
+      </c>
+      <c r="C503" t="n">
+        <v>43738</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B504" t="n">
+        <v>2782578</v>
+      </c>
+      <c r="C504" t="n">
+        <v>41173</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B505" t="n">
+        <v>2313392</v>
+      </c>
+      <c r="C505" t="n">
+        <v>34419</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B506" t="n">
+        <v>2557265</v>
+      </c>
+      <c r="C506" t="n">
+        <v>38251</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B507" t="n">
+        <v>2955843</v>
+      </c>
+      <c r="C507" t="n">
+        <v>44731</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B508" t="n">
+        <v>2976209</v>
+      </c>
+      <c r="C508" t="n">
+        <v>48873</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B509" t="n">
+        <v>2380377</v>
+      </c>
+      <c r="C509" t="n">
+        <v>40479</v>
       </c>
     </row>
   </sheetData>

--- a/code/df_tsa_ly.xlsx
+++ b/code/df_tsa_ly.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C509"/>
+  <dimension ref="A1:C523"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2173,7 +2173,7 @@
         <v>2766521</v>
       </c>
       <c r="C158" t="n">
-        <v>41361</v>
+        <v>41360</v>
       </c>
     </row>
     <row r="159">
@@ -2261,7 +2261,7 @@
         <v>2517202</v>
       </c>
       <c r="C166" t="n">
-        <v>35923</v>
+        <v>35922</v>
       </c>
     </row>
     <row r="167">
@@ -2305,7 +2305,7 @@
         <v>2705355</v>
       </c>
       <c r="C170" t="n">
-        <v>36077</v>
+        <v>36074</v>
       </c>
     </row>
     <row r="171">
@@ -2327,7 +2327,7 @@
         <v>2891240</v>
       </c>
       <c r="C172" t="n">
-        <v>44520</v>
+        <v>44515</v>
       </c>
     </row>
     <row r="173">
@@ -2338,7 +2338,7 @@
         <v>2614464</v>
       </c>
       <c r="C173" t="n">
-        <v>37580</v>
+        <v>37579</v>
       </c>
     </row>
     <row r="174">
@@ -2349,7 +2349,7 @@
         <v>3096797</v>
       </c>
       <c r="C174" t="n">
-        <v>44084</v>
+        <v>44079</v>
       </c>
     </row>
     <row r="175">
@@ -2371,7 +2371,7 @@
         <v>2508733</v>
       </c>
       <c r="C176" t="n">
-        <v>35019</v>
+        <v>35018</v>
       </c>
     </row>
     <row r="177">
@@ -2393,7 +2393,7 @@
         <v>2931282</v>
       </c>
       <c r="C178" t="n">
-        <v>41263</v>
+        <v>41262</v>
       </c>
     </row>
     <row r="179">
@@ -2415,7 +2415,7 @@
         <v>2624407</v>
       </c>
       <c r="C180" t="n">
-        <v>37197</v>
+        <v>37196</v>
       </c>
     </row>
     <row r="181">
@@ -2437,7 +2437,7 @@
         <v>2780012</v>
       </c>
       <c r="C182" t="n">
-        <v>47923</v>
+        <v>47920</v>
       </c>
     </row>
     <row r="183">
@@ -2448,7 +2448,7 @@
         <v>2402675</v>
       </c>
       <c r="C183" t="n">
-        <v>37179</v>
+        <v>37175</v>
       </c>
     </row>
     <row r="184">
@@ -2492,7 +2492,7 @@
         <v>2457591</v>
       </c>
       <c r="C187" t="n">
-        <v>37835</v>
+        <v>37834</v>
       </c>
     </row>
     <row r="188">
@@ -2514,7 +2514,7 @@
         <v>2917942</v>
       </c>
       <c r="C189" t="n">
-        <v>48811</v>
+        <v>48807</v>
       </c>
     </row>
     <row r="190">
@@ -2536,7 +2536,7 @@
         <v>2554687</v>
       </c>
       <c r="C191" t="n">
-        <v>36428</v>
+        <v>36426</v>
       </c>
     </row>
     <row r="192">
@@ -2547,7 +2547,7 @@
         <v>2873682</v>
       </c>
       <c r="C192" t="n">
-        <v>43397</v>
+        <v>43396</v>
       </c>
     </row>
     <row r="193">
@@ -2569,7 +2569,7 @@
         <v>2589889</v>
       </c>
       <c r="C194" t="n">
-        <v>38914</v>
+        <v>38913</v>
       </c>
     </row>
     <row r="195">
@@ -2613,7 +2613,7 @@
         <v>2614183</v>
       </c>
       <c r="C198" t="n">
-        <v>35610</v>
+        <v>35609</v>
       </c>
     </row>
     <row r="199">
@@ -2657,7 +2657,7 @@
         <v>3043973</v>
       </c>
       <c r="C202" t="n">
-        <v>45733</v>
+        <v>45732</v>
       </c>
     </row>
     <row r="203">
@@ -2668,7 +2668,7 @@
         <v>2886647</v>
       </c>
       <c r="C203" t="n">
-        <v>44331</v>
+        <v>44332</v>
       </c>
     </row>
     <row r="204">
@@ -2723,7 +2723,7 @@
         <v>2670276</v>
       </c>
       <c r="C208" t="n">
-        <v>38347</v>
+        <v>38345</v>
       </c>
     </row>
     <row r="209">
@@ -2800,7 +2800,7 @@
         <v>2640741</v>
       </c>
       <c r="C215" t="n">
-        <v>36905</v>
+        <v>36904</v>
       </c>
     </row>
     <row r="216">
@@ -2833,7 +2833,7 @@
         <v>2364019</v>
       </c>
       <c r="C218" t="n">
-        <v>32656</v>
+        <v>32655</v>
       </c>
     </row>
     <row r="219">
@@ -2855,7 +2855,7 @@
         <v>2893814</v>
       </c>
       <c r="C220" t="n">
-        <v>39717</v>
+        <v>39716</v>
       </c>
     </row>
     <row r="221">
@@ -2866,7 +2866,7 @@
         <v>2854458</v>
       </c>
       <c r="C221" t="n">
-        <v>42728</v>
+        <v>42727</v>
       </c>
     </row>
     <row r="222">
@@ -3020,7 +3020,7 @@
         <v>2667258</v>
       </c>
       <c r="C235" t="n">
-        <v>40231</v>
+        <v>40230</v>
       </c>
     </row>
     <row r="236">
@@ -3273,7 +3273,7 @@
         <v>2810804</v>
       </c>
       <c r="C258" t="n">
-        <v>41802</v>
+        <v>41801</v>
       </c>
     </row>
     <row r="259">
@@ -3295,7 +3295,7 @@
         <v>2004769</v>
       </c>
       <c r="C260" t="n">
-        <v>25444</v>
+        <v>25443</v>
       </c>
     </row>
     <row r="261">
@@ -3449,7 +3449,7 @@
         <v>2005123</v>
       </c>
       <c r="C274" t="n">
-        <v>27396</v>
+        <v>27395</v>
       </c>
     </row>
     <row r="275">
@@ -3834,7 +3834,7 @@
         <v>2015706</v>
       </c>
       <c r="C309" t="n">
-        <v>26844</v>
+        <v>26843</v>
       </c>
     </row>
     <row r="310">
@@ -3955,7 +3955,7 @@
         <v>1902157</v>
       </c>
       <c r="C320" t="n">
-        <v>28049</v>
+        <v>28048</v>
       </c>
     </row>
     <row r="321">
@@ -3977,7 +3977,7 @@
         <v>2349327</v>
       </c>
       <c r="C322" t="n">
-        <v>34145</v>
+        <v>34144</v>
       </c>
     </row>
     <row r="323">
@@ -3988,7 +3988,7 @@
         <v>1816617</v>
       </c>
       <c r="C323" t="n">
-        <v>22167</v>
+        <v>22166</v>
       </c>
     </row>
     <row r="324">
@@ -4010,7 +4010,7 @@
         <v>2493511</v>
       </c>
       <c r="C325" t="n">
-        <v>33245</v>
+        <v>33244</v>
       </c>
     </row>
     <row r="326">
@@ -4021,7 +4021,7 @@
         <v>2792495</v>
       </c>
       <c r="C326" t="n">
-        <v>38812</v>
+        <v>38811</v>
       </c>
     </row>
     <row r="327">
@@ -4065,7 +4065,7 @@
         <v>2675261</v>
       </c>
       <c r="C330" t="n">
-        <v>41045</v>
+        <v>41044</v>
       </c>
     </row>
     <row r="331">
@@ -4120,7 +4120,7 @@
         <v>3134613</v>
       </c>
       <c r="C335" t="n">
-        <v>49348</v>
+        <v>49342</v>
       </c>
     </row>
     <row r="336">
@@ -4142,7 +4142,7 @@
         <v>2233828</v>
       </c>
       <c r="C337" t="n">
-        <v>28828</v>
+        <v>28827</v>
       </c>
     </row>
     <row r="338">
@@ -4252,7 +4252,7 @@
         <v>2651654</v>
       </c>
       <c r="C347" t="n">
-        <v>39282</v>
+        <v>39281</v>
       </c>
     </row>
     <row r="348">
@@ -4274,7 +4274,7 @@
         <v>2586427</v>
       </c>
       <c r="C349" t="n">
-        <v>42677</v>
+        <v>42676</v>
       </c>
     </row>
     <row r="350">
@@ -4329,7 +4329,7 @@
         <v>2824905</v>
       </c>
       <c r="C354" t="n">
-        <v>46331</v>
+        <v>46330</v>
       </c>
     </row>
     <row r="355">
@@ -4351,7 +4351,7 @@
         <v>2769228</v>
       </c>
       <c r="C356" t="n">
-        <v>44866</v>
+        <v>44865</v>
       </c>
     </row>
     <row r="357">
@@ -4428,7 +4428,7 @@
         <v>2924593</v>
       </c>
       <c r="C363" t="n">
-        <v>47010</v>
+        <v>47009</v>
       </c>
     </row>
     <row r="364">
@@ -4439,7 +4439,7 @@
         <v>2811757</v>
       </c>
       <c r="C364" t="n">
-        <v>45780</v>
+        <v>45777</v>
       </c>
     </row>
     <row r="365">
@@ -4472,7 +4472,7 @@
         <v>2334465</v>
       </c>
       <c r="C367" t="n">
-        <v>36883</v>
+        <v>36882</v>
       </c>
     </row>
     <row r="368">
@@ -4505,7 +4505,7 @@
         <v>2817509</v>
       </c>
       <c r="C370" t="n">
-        <v>46858</v>
+        <v>46857</v>
       </c>
     </row>
     <row r="371">
@@ -4516,7 +4516,7 @@
         <v>2508517</v>
       </c>
       <c r="C371" t="n">
-        <v>36121</v>
+        <v>36118</v>
       </c>
     </row>
     <row r="372">
@@ -4538,7 +4538,7 @@
         <v>1900237</v>
       </c>
       <c r="C373" t="n">
-        <v>24811</v>
+        <v>24813</v>
       </c>
     </row>
     <row r="374">
@@ -4549,7 +4549,7 @@
         <v>2151117</v>
       </c>
       <c r="C374" t="n">
-        <v>29488</v>
+        <v>29487</v>
       </c>
     </row>
     <row r="375">
@@ -4560,7 +4560,7 @@
         <v>2206079</v>
       </c>
       <c r="C375" t="n">
-        <v>31671</v>
+        <v>31672</v>
       </c>
     </row>
     <row r="376">
@@ -4582,7 +4582,7 @@
         <v>2411470</v>
       </c>
       <c r="C377" t="n">
-        <v>33995</v>
+        <v>33994</v>
       </c>
     </row>
     <row r="378">
@@ -4659,7 +4659,7 @@
         <v>2231469</v>
       </c>
       <c r="C384" t="n">
-        <v>35392</v>
+        <v>35391</v>
       </c>
     </row>
     <row r="385">
@@ -4703,7 +4703,7 @@
         <v>2235021</v>
       </c>
       <c r="C388" t="n">
-        <v>28262</v>
+        <v>28261</v>
       </c>
     </row>
     <row r="389">
@@ -4714,7 +4714,7 @@
         <v>2243481</v>
       </c>
       <c r="C389" t="n">
-        <v>30629</v>
+        <v>30628</v>
       </c>
     </row>
     <row r="390">
@@ -4736,7 +4736,7 @@
         <v>1313323</v>
       </c>
       <c r="C391" t="n">
-        <v>29042</v>
+        <v>29040</v>
       </c>
     </row>
     <row r="392">
@@ -4747,7 +4747,7 @@
         <v>1830079</v>
       </c>
       <c r="C392" t="n">
-        <v>27149</v>
+        <v>27148</v>
       </c>
     </row>
     <row r="393">
@@ -4758,7 +4758,7 @@
         <v>1765468</v>
       </c>
       <c r="C393" t="n">
-        <v>20206</v>
+        <v>20205</v>
       </c>
     </row>
     <row r="394">
@@ -4769,7 +4769,7 @@
         <v>1879610</v>
       </c>
       <c r="C394" t="n">
-        <v>21687</v>
+        <v>21686</v>
       </c>
     </row>
     <row r="395">
@@ -4791,7 +4791,7 @@
         <v>2238006</v>
       </c>
       <c r="C396" t="n">
-        <v>30046</v>
+        <v>30045</v>
       </c>
     </row>
     <row r="397">
@@ -4802,7 +4802,7 @@
         <v>1729865</v>
       </c>
       <c r="C397" t="n">
-        <v>23917</v>
+        <v>23916</v>
       </c>
     </row>
     <row r="398">
@@ -4912,7 +4912,7 @@
         <v>1852752</v>
       </c>
       <c r="C407" t="n">
-        <v>23144</v>
+        <v>23143</v>
       </c>
     </row>
     <row r="408">
@@ -4923,7 +4923,7 @@
         <v>2074130</v>
       </c>
       <c r="C408" t="n">
-        <v>24927</v>
+        <v>24926</v>
       </c>
     </row>
     <row r="409">
@@ -4945,7 +4945,7 @@
         <v>2759407</v>
       </c>
       <c r="C410" t="n">
-        <v>39186</v>
+        <v>39184</v>
       </c>
     </row>
     <row r="411">
@@ -4956,7 +4956,7 @@
         <v>2186932</v>
       </c>
       <c r="C411" t="n">
-        <v>30366</v>
+        <v>30365</v>
       </c>
     </row>
     <row r="412">
@@ -4967,7 +4967,7 @@
         <v>2536292</v>
       </c>
       <c r="C412" t="n">
-        <v>41085</v>
+        <v>41083</v>
       </c>
     </row>
     <row r="413">
@@ -5022,7 +5022,7 @@
         <v>2650675</v>
       </c>
       <c r="C417" t="n">
-        <v>37888</v>
+        <v>37885</v>
       </c>
     </row>
     <row r="418">
@@ -5044,7 +5044,7 @@
         <v>2475455</v>
       </c>
       <c r="C419" t="n">
-        <v>37711</v>
+        <v>37710</v>
       </c>
     </row>
     <row r="420">
@@ -5055,7 +5055,7 @@
         <v>1996320</v>
       </c>
       <c r="C420" t="n">
-        <v>33086</v>
+        <v>33084</v>
       </c>
     </row>
     <row r="421">
@@ -5066,7 +5066,7 @@
         <v>1958051</v>
       </c>
       <c r="C421" t="n">
-        <v>24625</v>
+        <v>24624</v>
       </c>
     </row>
     <row r="422">
@@ -5088,7 +5088,7 @@
         <v>2647330</v>
       </c>
       <c r="C423" t="n">
-        <v>33551</v>
+        <v>33546</v>
       </c>
     </row>
     <row r="424">
@@ -5099,7 +5099,7 @@
         <v>2625251</v>
       </c>
       <c r="C424" t="n">
-        <v>36249</v>
+        <v>36247</v>
       </c>
     </row>
     <row r="425">
@@ -5110,7 +5110,7 @@
         <v>2190541</v>
       </c>
       <c r="C425" t="n">
-        <v>30589</v>
+        <v>30588</v>
       </c>
     </row>
     <row r="426">
@@ -5121,7 +5121,7 @@
         <v>2687408</v>
       </c>
       <c r="C426" t="n">
-        <v>38384</v>
+        <v>38383</v>
       </c>
     </row>
     <row r="427">
@@ -5132,7 +5132,7 @@
         <v>2432452</v>
       </c>
       <c r="C427" t="n">
-        <v>33403</v>
+        <v>33398</v>
       </c>
     </row>
     <row r="428">
@@ -5143,7 +5143,7 @@
         <v>1910452</v>
       </c>
       <c r="C428" t="n">
-        <v>23659</v>
+        <v>23660</v>
       </c>
     </row>
     <row r="429">
@@ -5165,7 +5165,7 @@
         <v>2615896</v>
       </c>
       <c r="C430" t="n">
-        <v>33291</v>
+        <v>33290</v>
       </c>
     </row>
     <row r="431">
@@ -5176,7 +5176,7 @@
         <v>2696932</v>
       </c>
       <c r="C431" t="n">
-        <v>37258</v>
+        <v>37245</v>
       </c>
     </row>
     <row r="432">
@@ -5198,7 +5198,7 @@
         <v>2781523</v>
       </c>
       <c r="C433" t="n">
-        <v>38769</v>
+        <v>38766</v>
       </c>
     </row>
     <row r="434">
@@ -5209,7 +5209,7 @@
         <v>2563627</v>
       </c>
       <c r="C434" t="n">
-        <v>35807</v>
+        <v>35805</v>
       </c>
     </row>
     <row r="435">
@@ -5220,7 +5220,7 @@
         <v>2056174</v>
       </c>
       <c r="C435" t="n">
-        <v>27725</v>
+        <v>27722</v>
       </c>
     </row>
     <row r="436">
@@ -5242,7 +5242,7 @@
         <v>2788748</v>
       </c>
       <c r="C437" t="n">
-        <v>38462</v>
+        <v>38459</v>
       </c>
     </row>
     <row r="438">
@@ -5253,7 +5253,7 @@
         <v>2854704</v>
       </c>
       <c r="C438" t="n">
-        <v>40510</v>
+        <v>40504</v>
       </c>
     </row>
     <row r="439">
@@ -5264,7 +5264,7 @@
         <v>2568085</v>
       </c>
       <c r="C439" t="n">
-        <v>35795</v>
+        <v>35796</v>
       </c>
     </row>
     <row r="440">
@@ -5275,7 +5275,7 @@
         <v>2765657</v>
       </c>
       <c r="C440" t="n">
-        <v>41584</v>
+        <v>41580</v>
       </c>
     </row>
     <row r="441">
@@ -5286,7 +5286,7 @@
         <v>2474964</v>
       </c>
       <c r="C441" t="n">
-        <v>42431</v>
+        <v>42430</v>
       </c>
     </row>
     <row r="442">
@@ -5297,7 +5297,7 @@
         <v>2424806</v>
       </c>
       <c r="C442" t="n">
-        <v>33968</v>
+        <v>33964</v>
       </c>
     </row>
     <row r="443">
@@ -5319,7 +5319,7 @@
         <v>2817785</v>
       </c>
       <c r="C444" t="n">
-        <v>40120</v>
+        <v>40116</v>
       </c>
     </row>
     <row r="445">
@@ -5330,7 +5330,7 @@
         <v>2766291</v>
       </c>
       <c r="C445" t="n">
-        <v>41648</v>
+        <v>41644</v>
       </c>
     </row>
     <row r="446">
@@ -5352,7 +5352,7 @@
         <v>2865969</v>
       </c>
       <c r="C447" t="n">
-        <v>41044</v>
+        <v>41041</v>
       </c>
     </row>
     <row r="448">
@@ -5363,7 +5363,7 @@
         <v>2641500</v>
       </c>
       <c r="C448" t="n">
-        <v>39561</v>
+        <v>39559</v>
       </c>
     </row>
     <row r="449">
@@ -5374,7 +5374,7 @@
         <v>2193195</v>
       </c>
       <c r="C449" t="n">
-        <v>30756</v>
+        <v>30753</v>
       </c>
     </row>
     <row r="450">
@@ -5385,7 +5385,7 @@
         <v>2379710</v>
       </c>
       <c r="C450" t="n">
-        <v>31349</v>
+        <v>31345</v>
       </c>
     </row>
     <row r="451">
@@ -5396,7 +5396,7 @@
         <v>2723798</v>
       </c>
       <c r="C451" t="n">
-        <v>36655</v>
+        <v>36652</v>
       </c>
     </row>
     <row r="452">
@@ -5407,7 +5407,7 @@
         <v>2744893</v>
       </c>
       <c r="C452" t="n">
-        <v>39191</v>
+        <v>39190</v>
       </c>
     </row>
     <row r="453">
@@ -5429,7 +5429,7 @@
         <v>2758600</v>
       </c>
       <c r="C454" t="n">
-        <v>39977</v>
+        <v>39975</v>
       </c>
     </row>
     <row r="455">
@@ -5440,7 +5440,7 @@
         <v>2533621</v>
       </c>
       <c r="C455" t="n">
-        <v>38748</v>
+        <v>38745</v>
       </c>
     </row>
     <row r="456">
@@ -5462,7 +5462,7 @@
         <v>2360739</v>
       </c>
       <c r="C457" t="n">
-        <v>33359</v>
+        <v>33356</v>
       </c>
     </row>
     <row r="458">
@@ -5473,7 +5473,7 @@
         <v>2710611</v>
       </c>
       <c r="C458" t="n">
-        <v>39226</v>
+        <v>39215</v>
       </c>
     </row>
     <row r="459">
@@ -5484,7 +5484,7 @@
         <v>2659561</v>
       </c>
       <c r="C459" t="n">
-        <v>40914</v>
+        <v>40910</v>
       </c>
     </row>
     <row r="460">
@@ -5495,7 +5495,7 @@
         <v>2274101</v>
       </c>
       <c r="C460" t="n">
-        <v>34246</v>
+        <v>34245</v>
       </c>
     </row>
     <row r="461">
@@ -5506,7 +5506,7 @@
         <v>2561932</v>
       </c>
       <c r="C461" t="n">
-        <v>39364</v>
+        <v>39362</v>
       </c>
     </row>
     <row r="462">
@@ -5517,7 +5517,7 @@
         <v>2705640</v>
       </c>
       <c r="C462" t="n">
-        <v>39229</v>
+        <v>39227</v>
       </c>
     </row>
     <row r="463">
@@ -5528,7 +5528,7 @@
         <v>2207180</v>
       </c>
       <c r="C463" t="n">
-        <v>30980</v>
+        <v>30977</v>
       </c>
     </row>
     <row r="464">
@@ -5539,7 +5539,7 @@
         <v>2278770</v>
       </c>
       <c r="C464" t="n">
-        <v>31497</v>
+        <v>31496</v>
       </c>
     </row>
     <row r="465">
@@ -5561,7 +5561,7 @@
         <v>2688395</v>
       </c>
       <c r="C466" t="n">
-        <v>40351</v>
+        <v>40347</v>
       </c>
     </row>
     <row r="467">
@@ -5572,7 +5572,7 @@
         <v>2269365</v>
       </c>
       <c r="C467" t="n">
-        <v>34315</v>
+        <v>34307</v>
       </c>
     </row>
     <row r="468">
@@ -5583,7 +5583,7 @@
         <v>2822290</v>
       </c>
       <c r="C468" t="n">
-        <v>40338</v>
+        <v>40333</v>
       </c>
     </row>
     <row r="469">
@@ -5594,7 +5594,7 @@
         <v>2606811</v>
       </c>
       <c r="C469" t="n">
-        <v>36816</v>
+        <v>36811</v>
       </c>
     </row>
     <row r="470">
@@ -5605,7 +5605,7 @@
         <v>2044781</v>
       </c>
       <c r="C470" t="n">
-        <v>27357</v>
+        <v>27356</v>
       </c>
     </row>
     <row r="471">
@@ -5616,7 +5616,7 @@
         <v>2251197</v>
       </c>
       <c r="C471" t="n">
-        <v>28680</v>
+        <v>28674</v>
       </c>
     </row>
     <row r="472">
@@ -5627,7 +5627,7 @@
         <v>2738409</v>
       </c>
       <c r="C472" t="n">
-        <v>36507</v>
+        <v>36502</v>
       </c>
     </row>
     <row r="473">
@@ -5638,7 +5638,7 @@
         <v>2705217</v>
       </c>
       <c r="C473" t="n">
-        <v>40580</v>
+        <v>40565</v>
       </c>
     </row>
     <row r="474">
@@ -5649,7 +5649,7 @@
         <v>2069600</v>
       </c>
       <c r="C474" t="n">
-        <v>31022</v>
+        <v>31016</v>
       </c>
     </row>
     <row r="475">
@@ -5660,7 +5660,7 @@
         <v>2796984</v>
       </c>
       <c r="C475" t="n">
-        <v>41018</v>
+        <v>41012</v>
       </c>
     </row>
     <row r="476">
@@ -5671,7 +5671,7 @@
         <v>2571543</v>
       </c>
       <c r="C476" t="n">
-        <v>37985</v>
+        <v>37974</v>
       </c>
     </row>
     <row r="477">
@@ -5682,7 +5682,7 @@
         <v>2055863</v>
       </c>
       <c r="C477" t="n">
-        <v>27278</v>
+        <v>27270</v>
       </c>
     </row>
     <row r="478">
@@ -5693,7 +5693,7 @@
         <v>2302381</v>
       </c>
       <c r="C478" t="n">
-        <v>29501</v>
+        <v>29494</v>
       </c>
     </row>
     <row r="479">
@@ -5704,7 +5704,7 @@
         <v>2740418</v>
       </c>
       <c r="C479" t="n">
-        <v>37707</v>
+        <v>37691</v>
       </c>
     </row>
     <row r="480">
@@ -5715,7 +5715,7 @@
         <v>2704682</v>
       </c>
       <c r="C480" t="n">
-        <v>40500</v>
+        <v>40485</v>
       </c>
     </row>
     <row r="481">
@@ -5726,7 +5726,7 @@
         <v>2093949</v>
       </c>
       <c r="C481" t="n">
-        <v>31127</v>
+        <v>31106</v>
       </c>
     </row>
     <row r="482">
@@ -5737,7 +5737,7 @@
         <v>2768606</v>
       </c>
       <c r="C482" t="n">
-        <v>41342</v>
+        <v>41336</v>
       </c>
     </row>
     <row r="483">
@@ -5748,7 +5748,7 @@
         <v>2539040</v>
       </c>
       <c r="C483" t="n">
-        <v>37818</v>
+        <v>37794</v>
       </c>
     </row>
     <row r="484">
@@ -5759,7 +5759,7 @@
         <v>2020266</v>
       </c>
       <c r="C484" t="n">
-        <v>27237</v>
+        <v>27219</v>
       </c>
     </row>
     <row r="485">
@@ -5770,7 +5770,7 @@
         <v>2264608</v>
       </c>
       <c r="C485" t="n">
-        <v>27658</v>
+        <v>27637</v>
       </c>
     </row>
     <row r="486">
@@ -5781,7 +5781,7 @@
         <v>2748380</v>
       </c>
       <c r="C486" t="n">
-        <v>36534</v>
+        <v>36529</v>
       </c>
     </row>
     <row r="487">
@@ -5792,7 +5792,7 @@
         <v>2643938</v>
       </c>
       <c r="C487" t="n">
-        <v>39810</v>
+        <v>39784</v>
       </c>
     </row>
     <row r="488">
@@ -5803,7 +5803,7 @@
         <v>2042664</v>
       </c>
       <c r="C488" t="n">
-        <v>31103</v>
+        <v>31090</v>
       </c>
     </row>
     <row r="489">
@@ -5814,7 +5814,7 @@
         <v>2741375</v>
       </c>
       <c r="C489" t="n">
-        <v>39830</v>
+        <v>39812</v>
       </c>
     </row>
     <row r="490">
@@ -5825,7 +5825,7 @@
         <v>2540806</v>
       </c>
       <c r="C490" t="n">
-        <v>35930</v>
+        <v>35916</v>
       </c>
     </row>
     <row r="491">
@@ -5836,7 +5836,7 @@
         <v>2040845</v>
       </c>
       <c r="C491" t="n">
-        <v>27842</v>
+        <v>27824</v>
       </c>
     </row>
     <row r="492">
@@ -5847,7 +5847,7 @@
         <v>2251410</v>
       </c>
       <c r="C492" t="n">
-        <v>30101</v>
+        <v>30078</v>
       </c>
     </row>
     <row r="493">
@@ -5858,7 +5858,7 @@
         <v>2701890</v>
       </c>
       <c r="C493" t="n">
-        <v>39265</v>
+        <v>39253</v>
       </c>
     </row>
     <row r="494">
@@ -5869,7 +5869,7 @@
         <v>2569907</v>
       </c>
       <c r="C494" t="n">
-        <v>40969</v>
+        <v>40951</v>
       </c>
     </row>
     <row r="495">
@@ -5880,7 +5880,7 @@
         <v>2088463</v>
       </c>
       <c r="C495" t="n">
-        <v>32954</v>
+        <v>32934</v>
       </c>
     </row>
     <row r="496">
@@ -5891,7 +5891,7 @@
         <v>2587640</v>
       </c>
       <c r="C496" t="n">
-        <v>41465</v>
+        <v>41436</v>
       </c>
     </row>
     <row r="497">
@@ -5902,7 +5902,7 @@
         <v>2661314</v>
       </c>
       <c r="C497" t="n">
-        <v>39722</v>
+        <v>39707</v>
       </c>
     </row>
     <row r="498">
@@ -5913,7 +5913,7 @@
         <v>2143904</v>
       </c>
       <c r="C498" t="n">
-        <v>30818</v>
+        <v>30802</v>
       </c>
     </row>
     <row r="499">
@@ -5924,7 +5924,7 @@
         <v>2399389</v>
       </c>
       <c r="C499" t="n">
-        <v>33087</v>
+        <v>33073</v>
       </c>
     </row>
     <row r="500">
@@ -5935,7 +5935,7 @@
         <v>2858330</v>
       </c>
       <c r="C500" t="n">
-        <v>39957</v>
+        <v>39947</v>
       </c>
     </row>
     <row r="501">
@@ -5946,7 +5946,7 @@
         <v>2796834</v>
       </c>
       <c r="C501" t="n">
-        <v>42837</v>
+        <v>42819</v>
       </c>
     </row>
     <row r="502">
@@ -5957,7 +5957,7 @@
         <v>2260950</v>
       </c>
       <c r="C502" t="n">
-        <v>36652</v>
+        <v>36635</v>
       </c>
     </row>
     <row r="503">
@@ -5968,7 +5968,7 @@
         <v>2887942</v>
       </c>
       <c r="C503" t="n">
-        <v>43738</v>
+        <v>43722</v>
       </c>
     </row>
     <row r="504">
@@ -5979,7 +5979,7 @@
         <v>2782578</v>
       </c>
       <c r="C504" t="n">
-        <v>41173</v>
+        <v>41159</v>
       </c>
     </row>
     <row r="505">
@@ -5990,7 +5990,7 @@
         <v>2313392</v>
       </c>
       <c r="C505" t="n">
-        <v>34419</v>
+        <v>34393</v>
       </c>
     </row>
     <row r="506">
@@ -6001,7 +6001,7 @@
         <v>2557265</v>
       </c>
       <c r="C506" t="n">
-        <v>38251</v>
+        <v>38201</v>
       </c>
     </row>
     <row r="507">
@@ -6012,7 +6012,7 @@
         <v>2955843</v>
       </c>
       <c r="C507" t="n">
-        <v>44731</v>
+        <v>44657</v>
       </c>
     </row>
     <row r="508">
@@ -6023,7 +6023,7 @@
         <v>2976209</v>
       </c>
       <c r="C508" t="n">
-        <v>48873</v>
+        <v>48835</v>
       </c>
     </row>
     <row r="509">
@@ -6034,7 +6034,161 @@
         <v>2380377</v>
       </c>
       <c r="C509" t="n">
-        <v>40479</v>
+        <v>40437</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B510" t="n">
+        <v>2418371</v>
+      </c>
+      <c r="C510" t="n">
+        <v>46881</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="2" t="n">
+        <v>46167</v>
+      </c>
+      <c r="B511" t="n">
+        <v>2818586</v>
+      </c>
+      <c r="C511" t="n">
+        <v>48120</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="2" t="n">
+        <v>46168</v>
+      </c>
+      <c r="B512" t="n">
+        <v>2507199</v>
+      </c>
+      <c r="C512" t="n">
+        <v>39696</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="2" t="n">
+        <v>46169</v>
+      </c>
+      <c r="B513" t="n">
+        <v>2374930</v>
+      </c>
+      <c r="C513" t="n">
+        <v>38394</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="2" t="n">
+        <v>46170</v>
+      </c>
+      <c r="B514" t="n">
+        <v>2661047</v>
+      </c>
+      <c r="C514" t="n">
+        <v>43012</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="2" t="n">
+        <v>46171</v>
+      </c>
+      <c r="B515" t="n">
+        <v>2689872</v>
+      </c>
+      <c r="C515" t="n">
+        <v>44215</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="2" t="n">
+        <v>46172</v>
+      </c>
+      <c r="B516" t="n">
+        <v>2307047</v>
+      </c>
+      <c r="C516" t="n">
+        <v>37532</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="2" t="n">
+        <v>46173</v>
+      </c>
+      <c r="B517" t="n">
+        <v>2818994</v>
+      </c>
+      <c r="C517" t="n">
+        <v>44662</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="2" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B518" t="n">
+        <v>2674187</v>
+      </c>
+      <c r="C518" t="n">
+        <v>41806</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="2" t="n">
+        <v>46175</v>
+      </c>
+      <c r="B519" t="n">
+        <v>2218178</v>
+      </c>
+      <c r="C519" t="n">
+        <v>33542</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B520" t="n">
+        <v>2400663</v>
+      </c>
+      <c r="C520" t="n">
+        <v>35494</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="2" t="n">
+        <v>46177</v>
+      </c>
+      <c r="B521" t="n">
+        <v>2773608</v>
+      </c>
+      <c r="C521" t="n">
+        <v>40938</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="2" t="n">
+        <v>46178</v>
+      </c>
+      <c r="B522" t="n">
+        <v>2710489</v>
+      </c>
+      <c r="C522" t="n">
+        <v>41652</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="2" t="n">
+        <v>46179</v>
+      </c>
+      <c r="B523" t="n">
+        <v>2359070</v>
+      </c>
+      <c r="C523" t="n">
+        <v>37265</v>
       </c>
     </row>
   </sheetData>
